--- a/IV_4.5K_T2.xlsx
+++ b/IV_4.5K_T2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2182,7 +2182,7 @@
         <v>31.25</v>
       </c>
       <c r="X25">
-        <v>5.4739999999999997E-2</v>
+        <v>5.475E-2</v>
       </c>
       <c r="Y25">
         <v>31.25</v>
@@ -2342,7 +2342,7 @@
         <v>34.375</v>
       </c>
       <c r="X27">
-        <v>6.0229999999999999E-2</v>
+        <v>6.021E-2</v>
       </c>
       <c r="Y27">
         <v>34.375</v>
@@ -2502,13 +2502,13 @@
         <v>37.5</v>
       </c>
       <c r="X29">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5680000000000002E-2</v>
       </c>
       <c r="Y29">
         <v>37.5</v>
       </c>
       <c r="Z29">
-        <v>6.6140000000000004E-2</v>
+        <v>6.6119999999999998E-2</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -2588,7 +2588,7 @@
         <v>39.0625</v>
       </c>
       <c r="Z30">
-        <v>6.8390000000000006E-2</v>
+        <v>6.8409999999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
@@ -2662,13 +2662,13 @@
         <v>40.625</v>
       </c>
       <c r="X31">
-        <v>7.1209999999999996E-2</v>
+        <v>7.1220000000000006E-2</v>
       </c>
       <c r="Y31">
         <v>40.625</v>
       </c>
       <c r="Z31">
-        <v>7.1150000000000005E-2</v>
+        <v>7.1160000000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
@@ -2730,7 +2730,7 @@
         <v>42.1875</v>
       </c>
       <c r="T32">
-        <v>7.3950000000000002E-2</v>
+        <v>7.3959999999999998E-2</v>
       </c>
       <c r="U32">
         <v>42.1875</v>
@@ -2822,7 +2822,7 @@
         <v>43.75</v>
       </c>
       <c r="X33">
-        <v>7.6679999999999998E-2</v>
+        <v>7.6689999999999994E-2</v>
       </c>
       <c r="Y33">
         <v>43.75</v>
@@ -2902,13 +2902,13 @@
         <v>45.3125</v>
       </c>
       <c r="X34">
-        <v>7.9420000000000004E-2</v>
+        <v>7.9399999999999998E-2</v>
       </c>
       <c r="Y34">
         <v>45.3125</v>
       </c>
       <c r="Z34">
-        <v>7.9329999999999998E-2</v>
+        <v>7.9320000000000002E-2</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
@@ -3062,13 +3062,13 @@
         <v>48.4375</v>
       </c>
       <c r="X36">
-        <v>8.4930000000000005E-2</v>
+        <v>8.4919999999999995E-2</v>
       </c>
       <c r="Y36">
         <v>48.4375</v>
       </c>
       <c r="Z36">
-        <v>8.4839999999999999E-2</v>
+        <v>8.4849999999999995E-2</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
@@ -3142,7 +3142,7 @@
         <v>50</v>
       </c>
       <c r="X37">
-        <v>8.7749999999999995E-2</v>
+        <v>8.7760000000000005E-2</v>
       </c>
       <c r="Y37">
         <v>50</v>
@@ -3228,7 +3228,7 @@
         <v>51.5625</v>
       </c>
       <c r="Z38">
-        <v>9.0399999999999994E-2</v>
+        <v>9.0410000000000004E-2</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
@@ -3302,7 +3302,7 @@
         <v>53.125</v>
       </c>
       <c r="X39">
-        <v>9.3219999999999997E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="Y39">
         <v>53.125</v>
@@ -3382,13 +3382,13 @@
         <v>54.6875</v>
       </c>
       <c r="X40">
-        <v>9.5979999999999996E-2</v>
+        <v>9.5960000000000004E-2</v>
       </c>
       <c r="Y40">
         <v>54.6875</v>
       </c>
       <c r="Z40">
-        <v>9.5890000000000003E-2</v>
+        <v>9.5899999999999999E-2</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>56.25</v>
       </c>
       <c r="X41">
-        <v>9.869E-2</v>
+        <v>9.8659999999999998E-2</v>
       </c>
       <c r="Y41">
         <v>56.25</v>
@@ -3542,7 +3542,7 @@
         <v>57.8125</v>
       </c>
       <c r="X42">
-        <v>0.10145</v>
+        <v>0.10145999999999999</v>
       </c>
       <c r="Y42">
         <v>57.8125</v>
@@ -3702,13 +3702,13 @@
         <v>60.9375</v>
       </c>
       <c r="X44">
-        <v>0.10692</v>
+        <v>0.10691000000000001</v>
       </c>
       <c r="Y44">
         <v>60.9375</v>
       </c>
       <c r="Z44">
-        <v>0.10685</v>
+        <v>0.10684</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
@@ -3782,7 +3782,7 @@
         <v>62.5</v>
       </c>
       <c r="X45">
-        <v>0.10967</v>
+        <v>0.10968</v>
       </c>
       <c r="Y45">
         <v>62.5</v>
@@ -3862,13 +3862,13 @@
         <v>64.0625</v>
       </c>
       <c r="X46">
-        <v>0.11243</v>
+        <v>0.11244</v>
       </c>
       <c r="Y46">
         <v>64.0625</v>
       </c>
       <c r="Z46">
-        <v>0.11239</v>
+        <v>0.1124</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -3912,7 +3912,7 @@
         <v>65.625</v>
       </c>
       <c r="N47">
-        <v>0.11514000000000001</v>
+        <v>0.11512</v>
       </c>
       <c r="O47">
         <v>65.625</v>
@@ -3942,7 +3942,7 @@
         <v>65.625</v>
       </c>
       <c r="X47">
-        <v>0.11518</v>
+        <v>0.11521000000000001</v>
       </c>
       <c r="Y47">
         <v>65.625</v>
@@ -4022,13 +4022,13 @@
         <v>67.1875</v>
       </c>
       <c r="X48">
-        <v>0.1179</v>
+        <v>0.1181</v>
       </c>
       <c r="Y48">
         <v>67.1875</v>
       </c>
       <c r="Z48">
-        <v>0.11788</v>
+        <v>0.11788999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>70.3125</v>
       </c>
       <c r="X50">
-        <v>0.12336999999999999</v>
+        <v>0.12339</v>
       </c>
       <c r="Y50">
         <v>70.3125</v>
@@ -4262,7 +4262,7 @@
         <v>71.875</v>
       </c>
       <c r="X51">
-        <v>0.12612000000000001</v>
+        <v>0.12611</v>
       </c>
       <c r="Y51">
         <v>71.875</v>
@@ -4342,13 +4342,13 @@
         <v>73.4375</v>
       </c>
       <c r="X52">
-        <v>0.12886</v>
+        <v>0.12887999999999999</v>
       </c>
       <c r="Y52">
         <v>73.4375</v>
       </c>
       <c r="Z52">
-        <v>0.12884000000000001</v>
+        <v>0.12887999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -4428,7 +4428,7 @@
         <v>75</v>
       </c>
       <c r="Z53">
-        <v>0.13159000000000001</v>
+        <v>0.13161999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>76.5625</v>
       </c>
       <c r="X54">
-        <v>0.13433</v>
+        <v>0.13431999999999999</v>
       </c>
       <c r="Y54">
         <v>76.5625</v>
@@ -4582,13 +4582,13 @@
         <v>78.125</v>
       </c>
       <c r="X55">
-        <v>0.13708000000000001</v>
+        <v>0.1371</v>
       </c>
       <c r="Y55">
         <v>78.125</v>
       </c>
       <c r="Z55">
-        <v>0.13708000000000001</v>
+        <v>0.13711000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
@@ -4673,10 +4673,10 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>79.6875</v>
+        <v>81.25</v>
       </c>
       <c r="B57">
-        <v>0.13950000000000001</v>
+        <v>0.14258000000000001</v>
       </c>
       <c r="C57">
         <v>81.25</v>
@@ -4712,7 +4712,7 @@
         <v>79.6875</v>
       </c>
       <c r="N57">
-        <v>0.13952000000000001</v>
+        <v>0.13949</v>
       </c>
       <c r="O57">
         <v>81.25</v>
@@ -4742,7 +4742,7 @@
         <v>79.6875</v>
       </c>
       <c r="X57">
-        <v>0.13950000000000001</v>
+        <v>0.1396</v>
       </c>
       <c r="Y57">
         <v>79.6875</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>78.125</v>
+        <v>82.8125</v>
       </c>
       <c r="B58">
-        <v>0.13675999999999999</v>
+        <v>0.14529</v>
       </c>
       <c r="C58">
         <v>82.8125</v>
@@ -4828,15 +4828,15 @@
         <v>78.125</v>
       </c>
       <c r="Z58">
-        <v>0.13674</v>
+        <v>0.13675000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>76.5625</v>
+        <v>84.375</v>
       </c>
       <c r="B59">
-        <v>0.13403000000000001</v>
+        <v>0.14804999999999999</v>
       </c>
       <c r="C59">
         <v>84.375</v>
@@ -4902,7 +4902,7 @@
         <v>76.5625</v>
       </c>
       <c r="X59">
-        <v>0.13400999999999999</v>
+        <v>0.13402</v>
       </c>
       <c r="Y59">
         <v>76.5625</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>75</v>
+        <v>85.9375</v>
       </c>
       <c r="B60">
-        <v>0.13127</v>
+        <v>0.15079999999999999</v>
       </c>
       <c r="C60">
         <v>85.9375</v>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>73.4375</v>
+        <v>87.5</v>
       </c>
       <c r="B61">
-        <v>0.12856000000000001</v>
+        <v>0.15357999999999999</v>
       </c>
       <c r="C61">
         <v>87.5</v>
@@ -5062,7 +5062,7 @@
         <v>73.4375</v>
       </c>
       <c r="X61">
-        <v>0.12853999999999999</v>
+        <v>0.12855</v>
       </c>
       <c r="Y61">
         <v>73.4375</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>71.875</v>
+        <v>89.0625</v>
       </c>
       <c r="B62">
-        <v>0.12578</v>
+        <v>0.15634000000000001</v>
       </c>
       <c r="C62">
         <v>89.0625</v>
@@ -5148,15 +5148,15 @@
         <v>71.875</v>
       </c>
       <c r="Z62">
-        <v>0.12576000000000001</v>
+        <v>0.12576999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>70.3125</v>
+        <v>90.625</v>
       </c>
       <c r="B63">
-        <v>0.12307</v>
+        <v>0.15909000000000001</v>
       </c>
       <c r="C63">
         <v>90.625</v>
@@ -5222,21 +5222,21 @@
         <v>70.3125</v>
       </c>
       <c r="X63">
-        <v>0.12304</v>
+        <v>0.12302</v>
       </c>
       <c r="Y63">
         <v>70.3125</v>
       </c>
       <c r="Z63">
-        <v>0.12304</v>
+        <v>0.12302</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>68.75</v>
+        <v>92.1875</v>
       </c>
       <c r="B64">
-        <v>0.12031</v>
+        <v>0.16184999999999999</v>
       </c>
       <c r="C64">
         <v>92.1875</v>
@@ -5308,15 +5308,15 @@
         <v>68.75</v>
       </c>
       <c r="Z64">
-        <v>0.12028999999999999</v>
+        <v>0.12031</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>67.1875</v>
+        <v>93.75</v>
       </c>
       <c r="B65">
-        <v>0.11758</v>
+        <v>0.16458</v>
       </c>
       <c r="C65">
         <v>93.75</v>
@@ -5382,7 +5382,7 @@
         <v>67.1875</v>
       </c>
       <c r="X65">
-        <v>0.11755</v>
+        <v>0.11756</v>
       </c>
       <c r="Y65">
         <v>67.1875</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>65.625</v>
+        <v>95.3125</v>
       </c>
       <c r="B66">
-        <v>0.11484</v>
+        <v>0.16733999999999999</v>
       </c>
       <c r="C66">
         <v>95.3125</v>
@@ -5462,21 +5462,21 @@
         <v>65.625</v>
       </c>
       <c r="X66">
-        <v>0.11482000000000001</v>
+        <v>0.11481</v>
       </c>
       <c r="Y66">
         <v>65.625</v>
       </c>
       <c r="Z66">
-        <v>0.11477999999999999</v>
+        <v>0.11477</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>64.0625</v>
+        <v>96.875</v>
       </c>
       <c r="B67">
-        <v>0.11211</v>
+        <v>0.1701</v>
       </c>
       <c r="C67">
         <v>96.875</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>62.5</v>
+        <v>98.4375</v>
       </c>
       <c r="B68">
-        <v>0.10931</v>
+        <v>0.17285</v>
       </c>
       <c r="C68">
         <v>98.4375</v>
@@ -5628,15 +5628,15 @@
         <v>62.5</v>
       </c>
       <c r="Z68">
-        <v>0.10928</v>
+        <v>0.10927000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>60.9375</v>
+        <v>100</v>
       </c>
       <c r="B69">
-        <v>0.10661</v>
+        <v>0.17529</v>
       </c>
       <c r="C69">
         <v>100</v>
@@ -5690,7 +5690,7 @@
         <v>60.9375</v>
       </c>
       <c r="T69">
-        <v>0.10657</v>
+        <v>0.10657999999999999</v>
       </c>
       <c r="U69">
         <v>100</v>
@@ -5708,15 +5708,15 @@
         <v>60.9375</v>
       </c>
       <c r="Z69">
-        <v>0.10655000000000001</v>
+        <v>0.10654</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>59.375</v>
+        <v>98.4375</v>
       </c>
       <c r="B70">
-        <v>0.10384</v>
+        <v>0.17252999999999999</v>
       </c>
       <c r="C70">
         <v>98.4375</v>
@@ -5770,7 +5770,7 @@
         <v>59.375</v>
       </c>
       <c r="T70">
-        <v>0.10384</v>
+        <v>0.10382</v>
       </c>
       <c r="U70">
         <v>98.4375</v>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>57.8125</v>
+        <v>96.875</v>
       </c>
       <c r="B71">
-        <v>0.10112</v>
+        <v>0.16979</v>
       </c>
       <c r="C71">
         <v>96.875</v>
@@ -5850,7 +5850,7 @@
         <v>57.8125</v>
       </c>
       <c r="T71">
-        <v>0.10108</v>
+        <v>0.10105</v>
       </c>
       <c r="U71">
         <v>96.875</v>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>56.25</v>
+        <v>95.3125</v>
       </c>
       <c r="B72">
-        <v>9.8369999999999999E-2</v>
+        <v>0.16702</v>
       </c>
       <c r="C72">
         <v>95.3125</v>
@@ -5948,15 +5948,15 @@
         <v>56.25</v>
       </c>
       <c r="Z72">
-        <v>9.8299999999999998E-2</v>
+        <v>9.8309999999999995E-2</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>54.6875</v>
+        <v>93.75</v>
       </c>
       <c r="B73">
-        <v>9.5649999999999999E-2</v>
+        <v>0.1643</v>
       </c>
       <c r="C73">
         <v>93.75</v>
@@ -6022,7 +6022,7 @@
         <v>54.6875</v>
       </c>
       <c r="X73">
-        <v>9.5610000000000001E-2</v>
+        <v>9.5600000000000004E-2</v>
       </c>
       <c r="Y73">
         <v>54.6875</v>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>53.125</v>
+        <v>92.1875</v>
       </c>
       <c r="B74">
-        <v>9.2899999999999996E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="C74">
         <v>92.1875</v>
@@ -6072,7 +6072,7 @@
         <v>53.125</v>
       </c>
       <c r="N74">
-        <v>9.2829999999999996E-2</v>
+        <v>9.2840000000000006E-2</v>
       </c>
       <c r="O74">
         <v>92.1875</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>51.5625</v>
+        <v>90.625</v>
       </c>
       <c r="B75">
-        <v>9.0160000000000004E-2</v>
+        <v>0.15876999999999999</v>
       </c>
       <c r="C75">
         <v>90.625</v>
@@ -6182,21 +6182,21 @@
         <v>51.5625</v>
       </c>
       <c r="X75">
-        <v>9.0120000000000006E-2</v>
+        <v>9.0109999999999996E-2</v>
       </c>
       <c r="Y75">
         <v>51.5625</v>
       </c>
       <c r="Z75">
-        <v>9.01E-2</v>
+        <v>9.0109999999999996E-2</v>
       </c>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>50</v>
+        <v>89.0625</v>
       </c>
       <c r="B76">
-        <v>8.7340000000000001E-2</v>
+        <v>0.15598999999999999</v>
       </c>
       <c r="C76">
         <v>89.0625</v>
@@ -6273,10 +6273,10 @@
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>48.4375</v>
+        <v>87.5</v>
       </c>
       <c r="B77">
-        <v>8.4610000000000005E-2</v>
+        <v>0.15326000000000001</v>
       </c>
       <c r="C77">
         <v>87.5</v>
@@ -6342,21 +6342,21 @@
         <v>48.4375</v>
       </c>
       <c r="X77">
-        <v>8.4540000000000004E-2</v>
+        <v>8.455E-2</v>
       </c>
       <c r="Y77">
         <v>48.4375</v>
       </c>
       <c r="Z77">
-        <v>8.4519999999999998E-2</v>
+        <v>8.4529999999999994E-2</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>46.875</v>
+        <v>85.9375</v>
       </c>
       <c r="B78">
-        <v>8.1850000000000006E-2</v>
+        <v>0.15048</v>
       </c>
       <c r="C78">
         <v>85.9375</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>45.3125</v>
+        <v>84.375</v>
       </c>
       <c r="B79">
-        <v>7.9140000000000002E-2</v>
+        <v>0.14774000000000001</v>
       </c>
       <c r="C79">
         <v>84.375</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>43.75</v>
+        <v>82.8125</v>
       </c>
       <c r="B80">
-        <v>7.6380000000000003E-2</v>
+        <v>0.14499000000000001</v>
       </c>
       <c r="C80">
         <v>82.8125</v>
@@ -6582,7 +6582,7 @@
         <v>43.75</v>
       </c>
       <c r="X80">
-        <v>7.6319999999999999E-2</v>
+        <v>7.6350000000000001E-2</v>
       </c>
       <c r="Y80">
         <v>43.75</v>
@@ -6593,10 +6593,10 @@
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>42.1875</v>
+        <v>81.25</v>
       </c>
       <c r="B81">
-        <v>7.3649999999999993E-2</v>
+        <v>0.14227000000000001</v>
       </c>
       <c r="C81">
         <v>81.25</v>
@@ -6644,7 +6644,7 @@
         <v>81.25</v>
       </c>
       <c r="R81">
-        <v>0.14219000000000001</v>
+        <v>0.14219999999999999</v>
       </c>
       <c r="S81">
         <v>42.1875</v>
@@ -6662,21 +6662,21 @@
         <v>42.1875</v>
       </c>
       <c r="X81">
-        <v>7.3580000000000007E-2</v>
+        <v>7.356E-2</v>
       </c>
       <c r="Y81">
         <v>42.1875</v>
       </c>
       <c r="Z81">
-        <v>7.356E-2</v>
+        <v>7.3539999999999994E-2</v>
       </c>
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>40.625</v>
+        <v>79.6875</v>
       </c>
       <c r="B82">
-        <v>7.0889999999999995E-2</v>
+        <v>0.13950000000000001</v>
       </c>
       <c r="C82">
         <v>79.6875</v>
@@ -6742,7 +6742,7 @@
         <v>40.625</v>
       </c>
       <c r="X82">
-        <v>7.0830000000000004E-2</v>
+        <v>7.0860000000000006E-2</v>
       </c>
       <c r="Y82">
         <v>40.625</v>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>39.0625</v>
+        <v>78.125</v>
       </c>
       <c r="B83">
-        <v>6.8180000000000004E-2</v>
+        <v>0.13675999999999999</v>
       </c>
       <c r="C83">
         <v>78.125</v>
@@ -6792,7 +6792,7 @@
         <v>39.0625</v>
       </c>
       <c r="N83">
-        <v>6.8070000000000006E-2</v>
+        <v>6.8080000000000002E-2</v>
       </c>
       <c r="O83">
         <v>78.125</v>
@@ -6804,7 +6804,7 @@
         <v>78.125</v>
       </c>
       <c r="R83">
-        <v>0.13668</v>
+        <v>0.13669000000000001</v>
       </c>
       <c r="S83">
         <v>39.0625</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>37.5</v>
+        <v>76.5625</v>
       </c>
       <c r="B84">
-        <v>6.54E-2</v>
+        <v>0.13403000000000001</v>
       </c>
       <c r="C84">
         <v>76.5625</v>
@@ -6872,7 +6872,7 @@
         <v>37.5</v>
       </c>
       <c r="N84">
-        <v>6.5310000000000007E-2</v>
+        <v>6.5320000000000003E-2</v>
       </c>
       <c r="O84">
         <v>76.5625</v>
@@ -6902,7 +6902,7 @@
         <v>37.5</v>
       </c>
       <c r="X84">
-        <v>6.5329999999999999E-2</v>
+        <v>6.5320000000000003E-2</v>
       </c>
       <c r="Y84">
         <v>37.5</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>35.9375</v>
+        <v>75</v>
       </c>
       <c r="B85">
-        <v>6.2689999999999996E-2</v>
+        <v>0.13127</v>
       </c>
       <c r="C85">
         <v>75</v>
@@ -6964,7 +6964,7 @@
         <v>75</v>
       </c>
       <c r="R85">
-        <v>0.13120999999999999</v>
+        <v>0.13120000000000001</v>
       </c>
       <c r="S85">
         <v>35.9375</v>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>34.375</v>
+        <v>73.4375</v>
       </c>
       <c r="B86">
-        <v>5.9909999999999998E-2</v>
+        <v>0.12856000000000001</v>
       </c>
       <c r="C86">
         <v>73.4375</v>
@@ -7062,21 +7062,21 @@
         <v>34.375</v>
       </c>
       <c r="X86">
-        <v>5.9839999999999997E-2</v>
+        <v>5.9819999999999998E-2</v>
       </c>
       <c r="Y86">
         <v>34.375</v>
       </c>
       <c r="Z86">
-        <v>5.9839999999999997E-2</v>
+        <v>5.9859999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>32.8125</v>
+        <v>71.875</v>
       </c>
       <c r="B87">
-        <v>5.7169999999999999E-2</v>
+        <v>0.12578</v>
       </c>
       <c r="C87">
         <v>71.875</v>
@@ -7124,7 +7124,7 @@
         <v>71.875</v>
       </c>
       <c r="R87">
-        <v>0.12569</v>
+        <v>0.12570999999999999</v>
       </c>
       <c r="S87">
         <v>32.8125</v>
@@ -7142,21 +7142,21 @@
         <v>32.8125</v>
       </c>
       <c r="X87">
-        <v>5.7110000000000001E-2</v>
+        <v>5.7119999999999997E-2</v>
       </c>
       <c r="Y87">
         <v>32.8125</v>
       </c>
       <c r="Z87">
-        <v>5.7110000000000001E-2</v>
+        <v>5.7119999999999997E-2</v>
       </c>
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>31.25</v>
+        <v>70.3125</v>
       </c>
       <c r="B88">
-        <v>5.416E-2</v>
+        <v>0.12307</v>
       </c>
       <c r="C88">
         <v>70.3125</v>
@@ -7222,7 +7222,7 @@
         <v>31.25</v>
       </c>
       <c r="X88">
-        <v>5.4350000000000002E-2</v>
+        <v>5.4339999999999999E-2</v>
       </c>
       <c r="Y88">
         <v>31.25</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>29.6875</v>
+        <v>68.75</v>
       </c>
       <c r="B89">
-        <v>5.0070000000000003E-2</v>
+        <v>0.12031</v>
       </c>
       <c r="C89">
         <v>68.75</v>
@@ -7284,7 +7284,7 @@
         <v>68.75</v>
       </c>
       <c r="R89" s="1">
-        <v>0.12021999999999999</v>
+        <v>0.12023</v>
       </c>
       <c r="S89">
         <v>29.6875</v>
@@ -7308,15 +7308,15 @@
         <v>29.6875</v>
       </c>
       <c r="Z89">
-        <v>5.16E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>28.125</v>
+        <v>67.1875</v>
       </c>
       <c r="B90">
-        <v>4.3580000000000001E-2</v>
+        <v>0.11758</v>
       </c>
       <c r="C90">
         <v>67.1875</v>
@@ -7382,21 +7382,21 @@
         <v>28.125</v>
       </c>
       <c r="X90">
-        <v>4.888E-2</v>
+        <v>4.8860000000000001E-2</v>
       </c>
       <c r="Y90">
         <v>28.125</v>
       </c>
       <c r="Z90">
-        <v>4.8820000000000002E-2</v>
+        <v>4.8800000000000003E-2</v>
       </c>
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>26.5625</v>
+        <v>65.625</v>
       </c>
       <c r="B91">
-        <v>1.3440000000000001E-2</v>
+        <v>0.11484</v>
       </c>
       <c r="C91">
         <v>65.625</v>
@@ -7462,7 +7462,7 @@
         <v>26.5625</v>
       </c>
       <c r="X91">
-        <v>4.6149999999999997E-2</v>
+        <v>4.614E-2</v>
       </c>
       <c r="Y91">
         <v>26.5625</v>
@@ -7473,10 +7473,10 @@
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>25</v>
+        <v>64.0625</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.11211</v>
       </c>
       <c r="C92">
         <v>64.0625</v>
@@ -7542,7 +7542,7 @@
         <v>25</v>
       </c>
       <c r="X92">
-        <v>4.3409999999999997E-2</v>
+        <v>4.342E-2</v>
       </c>
       <c r="Y92">
         <v>25</v>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>23.4375</v>
+        <v>62.5</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.10931</v>
       </c>
       <c r="C93">
         <v>62.5</v>
@@ -7622,7 +7622,7 @@
         <v>23.4375</v>
       </c>
       <c r="X93">
-        <v>4.0660000000000002E-2</v>
+        <v>4.0649999999999999E-2</v>
       </c>
       <c r="Y93">
         <v>23.4375</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>21.875</v>
+        <v>60.9375</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.10661</v>
       </c>
       <c r="C94">
         <v>60.9375</v>
@@ -7684,7 +7684,7 @@
         <v>60.9375</v>
       </c>
       <c r="R94">
-        <v>0.10650999999999999</v>
+        <v>0.10648000000000001</v>
       </c>
       <c r="S94">
         <v>21.875</v>
@@ -7702,7 +7702,7 @@
         <v>21.875</v>
       </c>
       <c r="X94">
-        <v>3.7859999999999998E-2</v>
+        <v>3.7850000000000002E-2</v>
       </c>
       <c r="Y94">
         <v>21.875</v>
@@ -7713,10 +7713,10 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>20.3125</v>
+        <v>59.375</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>0.10384</v>
       </c>
       <c r="C95">
         <v>59.375</v>
@@ -7782,7 +7782,7 @@
         <v>20.3125</v>
       </c>
       <c r="X95">
-        <v>3.4909999999999997E-2</v>
+        <v>3.492E-2</v>
       </c>
       <c r="Y95">
         <v>20.3125</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>18.75</v>
+        <v>57.8125</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>0.10112</v>
       </c>
       <c r="C96">
         <v>57.8125</v>
@@ -7850,7 +7850,7 @@
         <v>18.75</v>
       </c>
       <c r="T96">
-        <v>3.1370000000000002E-2</v>
+        <v>3.1390000000000001E-2</v>
       </c>
       <c r="U96">
         <v>57.8125</v>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>17.1875</v>
+        <v>56.25</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>9.8369999999999999E-2</v>
       </c>
       <c r="C97">
         <v>56.25</v>
@@ -7936,7 +7936,7 @@
         <v>56.25</v>
       </c>
       <c r="V97">
-        <v>9.8350000000000007E-2</v>
+        <v>9.8320000000000005E-2</v>
       </c>
       <c r="W97">
         <v>17.1875</v>
@@ -7953,10 +7953,10 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>15.625</v>
+        <v>54.6875</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>9.5649999999999999E-2</v>
       </c>
       <c r="C98">
         <v>54.6875</v>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>14.0625</v>
+        <v>53.125</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="C99">
         <v>53.125</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>12.5</v>
+        <v>51.5625</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>9.0160000000000004E-2</v>
       </c>
       <c r="C100">
         <v>51.5625</v>
@@ -8176,7 +8176,7 @@
         <v>51.5625</v>
       </c>
       <c r="V100">
-        <v>9.0120000000000006E-2</v>
+        <v>9.0130000000000002E-2</v>
       </c>
       <c r="W100">
         <v>12.5</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10.9375</v>
+        <v>50</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>8.7340000000000001E-2</v>
       </c>
       <c r="C101">
         <v>50</v>
@@ -8273,10 +8273,10 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9.375</v>
+        <v>48.4375</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>8.4610000000000005E-2</v>
       </c>
       <c r="C102">
         <v>48.4375</v>
@@ -8336,13 +8336,13 @@
         <v>48.4375</v>
       </c>
       <c r="V102">
-        <v>8.4540000000000004E-2</v>
+        <v>8.4559999999999996E-2</v>
       </c>
       <c r="W102">
         <v>9.375</v>
       </c>
       <c r="X102" s="1">
-        <v>7.7522099999999998E-4</v>
+        <v>6.8336570000000004E-4</v>
       </c>
       <c r="Y102">
         <v>9.375</v>
@@ -8353,10 +8353,10 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>7.8125</v>
+        <v>46.875</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>8.1850000000000006E-2</v>
       </c>
       <c r="C103">
         <v>46.875</v>
@@ -8422,7 +8422,7 @@
         <v>7.8125</v>
       </c>
       <c r="X103" s="1">
-        <v>1.7227099999999999E-4</v>
+        <v>2.57853E-4</v>
       </c>
       <c r="Y103">
         <v>7.8125</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>6.25</v>
+        <v>45.3125</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>7.9140000000000002E-2</v>
       </c>
       <c r="C104">
         <v>45.3125</v>
@@ -8502,7 +8502,7 @@
         <v>6.25</v>
       </c>
       <c r="X104" s="1">
-        <v>4.3067800000000001E-5</v>
+        <v>3.3513000000000003E-5</v>
       </c>
       <c r="Y104">
         <v>6.25</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>4.6875</v>
+        <v>43.75</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>7.6380000000000003E-2</v>
       </c>
       <c r="C105" s="1">
         <v>43.75</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>3.125</v>
+        <v>42.1875</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>7.3649999999999993E-2</v>
       </c>
       <c r="C106" s="1">
         <v>42.1875</v>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>1.5625</v>
+        <v>40.625</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>7.0889999999999995E-2</v>
       </c>
       <c r="C107">
         <v>40.625</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>0</v>
+        <v>39.0625</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>6.8180000000000004E-2</v>
       </c>
       <c r="C108">
         <v>39.0625</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>-1.5625</v>
+        <v>37.5</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>6.54E-2</v>
       </c>
       <c r="C109" s="1">
         <v>37.5</v>
@@ -8913,10 +8913,10 @@
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>-3.125</v>
+        <v>35.9375</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>6.2689999999999996E-2</v>
       </c>
       <c r="C110" s="1">
         <v>35.9375</v>
@@ -8993,10 +8993,10 @@
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>-4.6875</v>
+        <v>34.375</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>5.9909999999999998E-2</v>
       </c>
       <c r="C111" s="1">
         <v>34.375</v>
@@ -9073,10 +9073,10 @@
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>-6.25</v>
+        <v>32.8125</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5.7169999999999999E-2</v>
       </c>
       <c r="C112" s="1">
         <v>32.8125</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>-7.8125</v>
+        <v>31.25</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>5.416E-2</v>
       </c>
       <c r="C113" s="1">
         <v>31.25</v>
@@ -9233,10 +9233,10 @@
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>-9.375</v>
+        <v>29.6875</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>5.0070000000000003E-2</v>
       </c>
       <c r="C114" s="1">
         <v>29.6875</v>
@@ -9313,10 +9313,10 @@
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>-10.9375</v>
+        <v>28.125</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>4.3580000000000001E-2</v>
       </c>
       <c r="C115" s="1">
         <v>28.125</v>
@@ -9393,10 +9393,10 @@
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>-12.5</v>
+        <v>26.5625</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1.3440000000000001E-2</v>
       </c>
       <c r="C116" s="1">
         <v>26.5625</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>-14.0625</v>
+        <v>25</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -9553,7 +9553,7 @@
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>-15.625</v>
+        <v>23.4375</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -9633,7 +9633,7 @@
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>-17.1875</v>
+        <v>21.875</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -9713,7 +9713,7 @@
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>-18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>-20.3125</v>
+        <v>18.75</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>-21.875</v>
+        <v>17.1875</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -9953,7 +9953,7 @@
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>-23.4375</v>
+        <v>15.625</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -10022,7 +10022,7 @@
         <v>-23.4375</v>
       </c>
       <c r="X123">
-        <v>-4.0590000000000001E-2</v>
+        <v>-4.061E-2</v>
       </c>
       <c r="Y123">
         <v>-23.4375</v>
@@ -10033,7 +10033,7 @@
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>-25</v>
+        <v>14.0625</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>-25</v>
       </c>
       <c r="X124">
-        <v>-4.367E-2</v>
+        <v>-4.3679999999999997E-2</v>
       </c>
       <c r="Y124">
         <v>-25</v>
@@ -10113,7 +10113,7 @@
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>-26.5625</v>
+        <v>12.5</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -10193,7 +10193,7 @@
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>-28.125</v>
+        <v>10.9375</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -10262,7 +10262,7 @@
         <v>-28.125</v>
       </c>
       <c r="X126">
-        <v>-4.9230000000000003E-2</v>
+        <v>-4.922E-2</v>
       </c>
       <c r="Y126">
         <v>-28.125</v>
@@ -10273,7 +10273,7 @@
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>-29.6875</v>
+        <v>9.375</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         <v>-29.6875</v>
       </c>
       <c r="X127">
-        <v>-5.1950000000000003E-2</v>
+        <v>-5.1959999999999999E-2</v>
       </c>
       <c r="Y127">
         <v>-29.6875</v>
@@ -10353,7 +10353,7 @@
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>-31.25</v>
+        <v>7.8125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -10422,7 +10422,7 @@
         <v>-31.25</v>
       </c>
       <c r="X128">
-        <v>-5.4719999999999998E-2</v>
+        <v>-5.475E-2</v>
       </c>
       <c r="Y128">
         <v>-31.25</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>-32.8125</v>
+        <v>6.25</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>-34.375</v>
+        <v>4.6875</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -10582,18 +10582,18 @@
         <v>-34.375</v>
       </c>
       <c r="X130">
-        <v>-6.021E-2</v>
+        <v>-6.0220000000000003E-2</v>
       </c>
       <c r="Y130">
         <v>-34.375</v>
       </c>
       <c r="Z130">
-        <v>-6.0310000000000002E-2</v>
+        <v>-6.0290000000000003E-2</v>
       </c>
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>-35.9375</v>
+        <v>3.125</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -10662,18 +10662,18 @@
         <v>-35.9375</v>
       </c>
       <c r="X131">
-        <v>-6.2920000000000004E-2</v>
+        <v>-6.293E-2</v>
       </c>
       <c r="Y131">
         <v>-35.9375</v>
       </c>
       <c r="Z131">
-        <v>-6.2899999999999998E-2</v>
+        <v>-6.3100000000000003E-2</v>
       </c>
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>-37.5</v>
+        <v>1.5625</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -10753,7 +10753,7 @@
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>-39.0625</v>
+        <v>0</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -10828,12 +10828,12 @@
         <v>-39.0625</v>
       </c>
       <c r="Z133">
-        <v>-6.8129999999999996E-2</v>
+        <v>-6.812E-2</v>
       </c>
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>-40.625</v>
+        <v>-1.5625</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -10872,7 +10872,7 @@
         <v>-40.625</v>
       </c>
       <c r="N134">
-        <v>-7.1230000000000002E-2</v>
+        <v>-7.1220000000000006E-2</v>
       </c>
       <c r="O134">
         <v>-1.5625</v>
@@ -10902,7 +10902,7 @@
         <v>-40.625</v>
       </c>
       <c r="X134">
-        <v>-7.1169999999999997E-2</v>
+        <v>-7.1150000000000005E-2</v>
       </c>
       <c r="Y134">
         <v>-40.625</v>
@@ -10913,7 +10913,7 @@
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>-42.1875</v>
+        <v>-3.125</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -10988,12 +10988,12 @@
         <v>-42.1875</v>
       </c>
       <c r="Z135">
-        <v>-7.3950000000000002E-2</v>
+        <v>-7.3959999999999998E-2</v>
       </c>
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>-43.75</v>
+        <v>-4.6875</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -11062,7 +11062,7 @@
         <v>-43.75</v>
       </c>
       <c r="X136">
-        <v>-7.6660000000000006E-2</v>
+        <v>-7.6670000000000002E-2</v>
       </c>
       <c r="Y136">
         <v>-43.75</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>-45.3125</v>
+        <v>-6.25</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -11142,21 +11142,21 @@
         <v>-45.3125</v>
       </c>
       <c r="X137">
-        <v>-7.9420000000000004E-2</v>
+        <v>-7.9439999999999997E-2</v>
       </c>
       <c r="Y137">
         <v>-45.3125</v>
       </c>
       <c r="Z137">
-        <v>-7.9420000000000004E-2</v>
+        <v>-7.9439999999999997E-2</v>
       </c>
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>-46.875</v>
+        <v>-7.8125</v>
       </c>
       <c r="B138" s="1">
-        <v>-1.0767E-4</v>
+        <v>0</v>
       </c>
       <c r="C138" s="1">
         <v>-7.8125</v>
@@ -11222,7 +11222,7 @@
         <v>-46.875</v>
       </c>
       <c r="X138">
-        <v>-8.2150000000000001E-2</v>
+        <v>-8.2140000000000005E-2</v>
       </c>
       <c r="Y138">
         <v>-46.875</v>
@@ -11233,10 +11233,10 @@
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>-48.4375</v>
+        <v>-9.375</v>
       </c>
       <c r="B139">
-        <v>-8.3750000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="C139" s="1">
         <v>-9.375</v>
@@ -11302,7 +11302,7 @@
         <v>-48.4375</v>
       </c>
       <c r="X139">
-        <v>-8.4909999999999999E-2</v>
+        <v>-8.4919999999999995E-2</v>
       </c>
       <c r="Y139">
         <v>-48.4375</v>
@@ -11313,10 +11313,10 @@
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>-50</v>
+        <v>-10.9375</v>
       </c>
       <c r="B140">
-        <v>-8.7660000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C140" s="1">
         <v>-10.9375</v>
@@ -11388,15 +11388,15 @@
         <v>-50</v>
       </c>
       <c r="Z140">
-        <v>-8.7639999999999996E-2</v>
+        <v>-8.7620000000000003E-2</v>
       </c>
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>-51.5625</v>
+        <v>-12.5</v>
       </c>
       <c r="B141">
-        <v>-9.042E-2</v>
+        <v>0</v>
       </c>
       <c r="C141" s="1">
         <v>-12.5</v>
@@ -11468,15 +11468,15 @@
         <v>-51.5625</v>
       </c>
       <c r="Z141">
-        <v>-9.0459999999999999E-2</v>
+        <v>-9.0469999999999995E-2</v>
       </c>
     </row>
     <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>-53.125</v>
+        <v>-14.0625</v>
       </c>
       <c r="B142">
-        <v>-9.3160000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="C142" s="1">
         <v>-14.0625</v>
@@ -11542,7 +11542,7 @@
         <v>-53.125</v>
       </c>
       <c r="X142">
-        <v>-9.3200000000000005E-2</v>
+        <v>-9.3219999999999997E-2</v>
       </c>
       <c r="Y142">
         <v>-53.125</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>-54.6875</v>
+        <v>-15.625</v>
       </c>
       <c r="B143">
-        <v>-9.5909999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="C143" s="1">
         <v>-15.625</v>
@@ -11592,7 +11592,7 @@
         <v>-54.6875</v>
       </c>
       <c r="N143">
-        <v>-9.5960000000000004E-2</v>
+        <v>-9.5979999999999996E-2</v>
       </c>
       <c r="O143">
         <v>-15.625</v>
@@ -11622,7 +11622,7 @@
         <v>-54.6875</v>
       </c>
       <c r="X143">
-        <v>-9.5960000000000004E-2</v>
+        <v>-9.597E-2</v>
       </c>
       <c r="Y143">
         <v>-54.6875</v>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>-56.25</v>
+        <v>-17.1875</v>
       </c>
       <c r="B144">
-        <v>-9.8650000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C144" s="1">
         <v>-17.1875</v>
@@ -11713,10 +11713,10 @@
     </row>
     <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>-57.8125</v>
+        <v>-18.75</v>
       </c>
       <c r="B145">
-        <v>-0.1014</v>
+        <v>0</v>
       </c>
       <c r="C145">
         <v>-18.75</v>
@@ -11782,21 +11782,21 @@
         <v>-57.8125</v>
       </c>
       <c r="X145">
-        <v>-0.10145</v>
+        <v>-0.10144</v>
       </c>
       <c r="Y145">
         <v>-57.8125</v>
       </c>
       <c r="Z145">
-        <v>-0.10142</v>
+        <v>-0.10141</v>
       </c>
     </row>
     <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>-59.375</v>
+        <v>-20.3125</v>
       </c>
       <c r="B146">
-        <v>-0.10414</v>
+        <v>0</v>
       </c>
       <c r="C146">
         <v>-20.3125</v>
@@ -11873,10 +11873,10 @@
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>-60.9375</v>
+        <v>-21.875</v>
       </c>
       <c r="B147">
-        <v>-0.10689</v>
+        <v>0</v>
       </c>
       <c r="C147">
         <v>-21.875</v>
@@ -11942,21 +11942,21 @@
         <v>-60.9375</v>
       </c>
       <c r="X147">
-        <v>-0.10693999999999999</v>
+        <v>-0.10695</v>
       </c>
       <c r="Y147">
         <v>-60.9375</v>
       </c>
       <c r="Z147">
-        <v>-0.10692</v>
+        <v>-0.10691000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>-62.5</v>
+        <v>-23.4375</v>
       </c>
       <c r="B148">
-        <v>-0.10963000000000001</v>
+        <v>0</v>
       </c>
       <c r="C148">
         <v>-23.4375</v>
@@ -12022,7 +12022,7 @@
         <v>-62.5</v>
       </c>
       <c r="X148">
-        <v>-0.10967</v>
+        <v>-0.10965999999999999</v>
       </c>
       <c r="Y148">
         <v>-62.5</v>
@@ -12033,10 +12033,10 @@
     </row>
     <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>-64.0625</v>
+        <v>-25</v>
       </c>
       <c r="B149">
-        <v>-0.11239</v>
+        <v>0</v>
       </c>
       <c r="C149">
         <v>-25</v>
@@ -12108,15 +12108,15 @@
         <v>-64.0625</v>
       </c>
       <c r="Z149">
-        <v>-0.11241</v>
+        <v>-0.11242000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>-65.625</v>
+        <v>-26.5625</v>
       </c>
       <c r="B150">
-        <v>-0.11514000000000001</v>
+        <v>0</v>
       </c>
       <c r="C150">
         <v>-26.5625</v>
@@ -12182,7 +12182,7 @@
         <v>-65.625</v>
       </c>
       <c r="X150">
-        <v>-0.11516</v>
+        <v>-0.11516999999999999</v>
       </c>
       <c r="Y150">
         <v>-65.625</v>
@@ -12193,10 +12193,10 @@
     </row>
     <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>-67.1875</v>
+        <v>-28.125</v>
       </c>
       <c r="B151">
-        <v>-0.11788</v>
+        <v>0</v>
       </c>
       <c r="C151">
         <v>-28.125</v>
@@ -12262,21 +12262,21 @@
         <v>-67.1875</v>
       </c>
       <c r="X151">
-        <v>-0.11794</v>
+        <v>-0.11796</v>
       </c>
       <c r="Y151">
         <v>-67.1875</v>
       </c>
       <c r="Z151">
-        <v>-0.1179</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>-68.75</v>
+        <v>-29.6875</v>
       </c>
       <c r="B152">
-        <v>-0.12063</v>
+        <v>0</v>
       </c>
       <c r="C152">
         <v>-29.6875</v>
@@ -12342,7 +12342,7 @@
         <v>-68.75</v>
       </c>
       <c r="X152">
-        <v>-0.12068</v>
+        <v>-0.12067</v>
       </c>
       <c r="Y152">
         <v>-68.75</v>
@@ -12353,10 +12353,10 @@
     </row>
     <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>-70.3125</v>
+        <v>-31.25</v>
       </c>
       <c r="B153">
-        <v>-0.12339</v>
+        <v>0</v>
       </c>
       <c r="C153">
         <v>-31.25</v>
@@ -12433,10 +12433,10 @@
     </row>
     <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>-71.875</v>
+        <v>-32.8125</v>
       </c>
       <c r="B154">
-        <v>-0.12612000000000001</v>
+        <v>0</v>
       </c>
       <c r="C154">
         <v>-32.8125</v>
@@ -12502,21 +12502,21 @@
         <v>-71.875</v>
       </c>
       <c r="X154">
-        <v>-0.12617</v>
+        <v>-0.12619</v>
       </c>
       <c r="Y154">
         <v>-71.875</v>
       </c>
       <c r="Z154">
-        <v>-0.12609999999999999</v>
+        <v>-0.1263</v>
       </c>
     </row>
     <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>-73.4375</v>
+        <v>-34.375</v>
       </c>
       <c r="B155">
-        <v>-0.12887999999999999</v>
+        <v>0</v>
       </c>
       <c r="C155">
         <v>-34.375</v>
@@ -12552,7 +12552,7 @@
         <v>-73.4375</v>
       </c>
       <c r="N155">
-        <v>-0.12887999999999999</v>
+        <v>-0.12887000000000001</v>
       </c>
       <c r="O155">
         <v>-34.375</v>
@@ -12570,7 +12570,7 @@
         <v>-73.4375</v>
       </c>
       <c r="T155">
-        <v>-0.12892000000000001</v>
+        <v>-0.12891</v>
       </c>
       <c r="U155">
         <v>-34.375</v>
@@ -12593,10 +12593,10 @@
     </row>
     <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>-75</v>
+        <v>-35.9375</v>
       </c>
       <c r="B156">
-        <v>-0.13161999999999999</v>
+        <v>0</v>
       </c>
       <c r="C156">
         <v>-35.9375</v>
@@ -12662,7 +12662,7 @@
         <v>-75</v>
       </c>
       <c r="X156">
-        <v>-0.13167999999999999</v>
+        <v>-0.13170999999999999</v>
       </c>
       <c r="Y156">
         <v>-75</v>
@@ -12673,10 +12673,10 @@
     </row>
     <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>-76.5625</v>
+        <v>-37.5</v>
       </c>
       <c r="B157">
-        <v>-0.13435</v>
+        <v>0</v>
       </c>
       <c r="C157">
         <v>-37.5</v>
@@ -12742,21 +12742,21 @@
         <v>-76.5625</v>
       </c>
       <c r="X157">
-        <v>-0.13439000000000001</v>
+        <v>-0.13436999999999999</v>
       </c>
       <c r="Y157">
         <v>-76.5625</v>
       </c>
       <c r="Z157">
-        <v>-0.13435</v>
+        <v>-0.13433999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>-78.125</v>
+        <v>-39.0625</v>
       </c>
       <c r="B158">
-        <v>-0.13711000000000001</v>
+        <v>0</v>
       </c>
       <c r="C158">
         <v>-39.0625</v>
@@ -12822,21 +12822,21 @@
         <v>-78.125</v>
       </c>
       <c r="X158">
-        <v>-0.13714999999999999</v>
+        <v>-0.13716</v>
       </c>
       <c r="Y158">
         <v>-78.125</v>
       </c>
       <c r="Z158">
-        <v>-0.13708000000000001</v>
+        <v>-0.13707</v>
       </c>
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>-79.6875</v>
+        <v>-40.625</v>
       </c>
       <c r="B159">
-        <v>-0.13986000000000001</v>
+        <v>0</v>
       </c>
       <c r="C159">
         <v>-40.625</v>
@@ -12908,15 +12908,15 @@
         <v>-79.6875</v>
       </c>
       <c r="Z159">
-        <v>-0.13983999999999999</v>
+        <v>-0.13986000000000001</v>
       </c>
     </row>
     <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>-79.6875</v>
+        <v>-42.1875</v>
       </c>
       <c r="B160">
-        <v>-0.13954</v>
+        <v>0</v>
       </c>
       <c r="C160">
         <v>-42.1875</v>
@@ -12982,7 +12982,7 @@
         <v>-79.6875</v>
       </c>
       <c r="X160">
-        <v>-0.13950000000000001</v>
+        <v>-0.1394</v>
       </c>
       <c r="Y160">
         <v>-79.6875</v>
@@ -12993,10 +12993,10 @@
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>-78.125</v>
+        <v>-43.75</v>
       </c>
       <c r="B161">
-        <v>-0.1368</v>
+        <v>0</v>
       </c>
       <c r="C161">
         <v>-43.75</v>
@@ -13062,21 +13062,21 @@
         <v>-78.125</v>
       </c>
       <c r="X161">
-        <v>-0.13675999999999999</v>
+        <v>-0.13674</v>
       </c>
       <c r="Y161">
         <v>-78.125</v>
       </c>
       <c r="Z161">
-        <v>-0.13678000000000001</v>
+        <v>-0.13677</v>
       </c>
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>-76.5625</v>
+        <v>-45.3125</v>
       </c>
       <c r="B162">
-        <v>-0.13403000000000001</v>
+        <v>0</v>
       </c>
       <c r="C162">
         <v>-45.3125</v>
@@ -13153,10 +13153,10 @@
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>-75</v>
-      </c>
-      <c r="B163">
-        <v>-0.13128999999999999</v>
+        <v>-46.875</v>
+      </c>
+      <c r="B163" s="1">
+        <v>-1.0767E-4</v>
       </c>
       <c r="C163">
         <v>-46.875</v>
@@ -13222,21 +13222,21 @@
         <v>-75</v>
       </c>
       <c r="X163">
-        <v>-0.13127</v>
+        <v>-0.13125000000000001</v>
       </c>
       <c r="Y163">
         <v>-75</v>
       </c>
       <c r="Z163">
-        <v>-0.13131000000000001</v>
+        <v>-0.13131999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>-73.4375</v>
+        <v>-48.4375</v>
       </c>
       <c r="B164">
-        <v>-0.12856000000000001</v>
+        <v>-8.3750000000000005E-2</v>
       </c>
       <c r="C164">
         <v>-48.4375</v>
@@ -13302,21 +13302,21 @@
         <v>-73.4375</v>
       </c>
       <c r="X164">
-        <v>-0.12851000000000001</v>
+        <v>-0.12852</v>
       </c>
       <c r="Y164">
         <v>-73.4375</v>
       </c>
       <c r="Z164">
-        <v>-0.12856000000000001</v>
+        <v>-0.12855</v>
       </c>
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>-71.875</v>
+        <v>-50</v>
       </c>
       <c r="B165">
-        <v>-0.1258</v>
+        <v>-8.7660000000000002E-2</v>
       </c>
       <c r="C165">
         <v>-50</v>
@@ -13382,21 +13382,21 @@
         <v>-71.875</v>
       </c>
       <c r="X165">
-        <v>-0.12578</v>
+        <v>-0.12576000000000001</v>
       </c>
       <c r="Y165">
         <v>-71.875</v>
       </c>
       <c r="Z165">
-        <v>-0.12581999999999999</v>
+        <v>-0.1258</v>
       </c>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>-70.3125</v>
+        <v>-51.5625</v>
       </c>
       <c r="B166">
-        <v>-0.12304</v>
+        <v>-9.042E-2</v>
       </c>
       <c r="C166">
         <v>-51.5625</v>
@@ -13462,7 +13462,7 @@
         <v>-70.3125</v>
       </c>
       <c r="X166">
-        <v>-0.12302</v>
+        <v>-0.12300999999999999</v>
       </c>
       <c r="Y166">
         <v>-70.3125</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>-68.75</v>
+        <v>-53.125</v>
       </c>
       <c r="B167">
-        <v>-0.12033000000000001</v>
+        <v>-9.3160000000000007E-2</v>
       </c>
       <c r="C167">
         <v>-53.125</v>
@@ -13530,7 +13530,7 @@
         <v>-68.75</v>
       </c>
       <c r="T167">
-        <v>-0.12028999999999999</v>
+        <v>-0.12028</v>
       </c>
       <c r="U167">
         <v>-53.125</v>
@@ -13553,10 +13553,10 @@
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>-67.1875</v>
+        <v>-54.6875</v>
       </c>
       <c r="B168">
-        <v>-0.11755</v>
+        <v>-9.5909999999999995E-2</v>
       </c>
       <c r="C168">
         <v>-54.6875</v>
@@ -13610,7 +13610,7 @@
         <v>-67.1875</v>
       </c>
       <c r="T168">
-        <v>-0.11758</v>
+        <v>-0.11761000000000001</v>
       </c>
       <c r="U168">
         <v>-54.6875</v>
@@ -13628,15 +13628,15 @@
         <v>-67.1875</v>
       </c>
       <c r="Z168">
-        <v>-0.1176</v>
+        <v>-0.11749999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>-65.625</v>
+        <v>-56.25</v>
       </c>
       <c r="B169">
-        <v>-0.11482000000000001</v>
+        <v>-9.8650000000000002E-2</v>
       </c>
       <c r="C169">
         <v>-56.25</v>
@@ -13702,21 +13702,21 @@
         <v>-65.625</v>
       </c>
       <c r="X169">
-        <v>-0.11482000000000001</v>
+        <v>-0.11481</v>
       </c>
       <c r="Y169">
         <v>-65.625</v>
       </c>
       <c r="Z169">
-        <v>-0.11484</v>
+        <v>-0.11482000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>-64.0625</v>
+        <v>-57.8125</v>
       </c>
       <c r="B170">
-        <v>-0.11206000000000001</v>
+        <v>-0.1014</v>
       </c>
       <c r="C170">
         <v>-57.8125</v>
@@ -13764,7 +13764,7 @@
         <v>-57.8125</v>
       </c>
       <c r="R170">
-        <v>-0.10142</v>
+        <v>-0.10143000000000001</v>
       </c>
       <c r="S170">
         <v>-64.0625</v>
@@ -13782,7 +13782,7 @@
         <v>-64.0625</v>
       </c>
       <c r="X170">
-        <v>-0.11208</v>
+        <v>-0.11207</v>
       </c>
       <c r="Y170">
         <v>-64.0625</v>
@@ -13793,10 +13793,10 @@
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>-62.5</v>
+        <v>-59.375</v>
       </c>
       <c r="B171">
-        <v>-0.10931</v>
+        <v>-0.10414</v>
       </c>
       <c r="C171">
         <v>-59.375</v>
@@ -13862,13 +13862,13 @@
         <v>-62.5</v>
       </c>
       <c r="X171">
-        <v>-0.10933</v>
+        <v>-0.10935</v>
       </c>
       <c r="Y171">
         <v>-62.5</v>
       </c>
       <c r="Z171">
-        <v>-0.10935</v>
+        <v>-0.10936</v>
       </c>
     </row>
     <row r="172" spans="1:26" x14ac:dyDescent="0.25">
@@ -13876,7 +13876,7 @@
         <v>-60.9375</v>
       </c>
       <c r="B172">
-        <v>-0.10657</v>
+        <v>-0.10689</v>
       </c>
       <c r="C172">
         <v>-60.9375</v>
@@ -13924,7 +13924,7 @@
         <v>-60.9375</v>
       </c>
       <c r="R172">
-        <v>-0.10692</v>
+        <v>-0.1069</v>
       </c>
       <c r="S172">
         <v>-60.9375</v>
@@ -13942,7 +13942,7 @@
         <v>-60.9375</v>
       </c>
       <c r="X172">
-        <v>-0.10659</v>
+        <v>-0.10661</v>
       </c>
       <c r="Y172">
         <v>-60.9375</v>
@@ -13953,10 +13953,10 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>-59.375</v>
+        <v>-62.5</v>
       </c>
       <c r="B173">
-        <v>-0.10384</v>
+        <v>-0.10963000000000001</v>
       </c>
       <c r="C173">
         <v>-62.5</v>
@@ -14022,21 +14022,21 @@
         <v>-59.375</v>
       </c>
       <c r="X173">
-        <v>-0.10384</v>
+        <v>-0.10385</v>
       </c>
       <c r="Y173">
         <v>-59.375</v>
       </c>
       <c r="Z173">
-        <v>-0.10385999999999999</v>
+        <v>-0.10387</v>
       </c>
     </row>
     <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>-57.8125</v>
+        <v>-64.0625</v>
       </c>
       <c r="B174">
-        <v>-0.10108</v>
+        <v>-0.11239</v>
       </c>
       <c r="C174">
         <v>-64.0625</v>
@@ -14108,15 +14108,15 @@
         <v>-57.8125</v>
       </c>
       <c r="Z174">
-        <v>-0.1011</v>
+        <v>-0.10100000000000001</v>
       </c>
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>-56.25</v>
+        <v>-65.625</v>
       </c>
       <c r="B175">
-        <v>-9.8350000000000007E-2</v>
+        <v>-0.11514000000000001</v>
       </c>
       <c r="C175">
         <v>-65.625</v>
@@ -14182,7 +14182,7 @@
         <v>-56.25</v>
       </c>
       <c r="X175">
-        <v>-9.8390000000000005E-2</v>
+        <v>-9.8360000000000003E-2</v>
       </c>
       <c r="Y175">
         <v>-56.25</v>
@@ -14193,10 +14193,10 @@
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>-54.6875</v>
+        <v>-67.1875</v>
       </c>
       <c r="B176">
-        <v>-9.5589999999999994E-2</v>
+        <v>-0.11788</v>
       </c>
       <c r="C176">
         <v>-67.1875</v>
@@ -14232,7 +14232,7 @@
         <v>-54.6875</v>
       </c>
       <c r="N176">
-        <v>-9.5649999999999999E-2</v>
+        <v>-9.5640000000000003E-2</v>
       </c>
       <c r="O176">
         <v>-67.1875</v>
@@ -14262,7 +14262,7 @@
         <v>-54.6875</v>
       </c>
       <c r="X176">
-        <v>-9.5610000000000001E-2</v>
+        <v>-9.5649999999999999E-2</v>
       </c>
       <c r="Y176">
         <v>-54.6875</v>
@@ -14273,10 +14273,10 @@
     </row>
     <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>-53.125</v>
+        <v>-68.75</v>
       </c>
       <c r="B177">
-        <v>-9.2850000000000002E-2</v>
+        <v>-0.12063</v>
       </c>
       <c r="C177">
         <v>-68.75</v>
@@ -14348,15 +14348,15 @@
         <v>-53.125</v>
       </c>
       <c r="Z177">
-        <v>-9.2899999999999996E-2</v>
+        <v>-9.2880000000000004E-2</v>
       </c>
     </row>
     <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>-51.5625</v>
+        <v>-70.3125</v>
       </c>
       <c r="B178">
-        <v>-9.0120000000000006E-2</v>
+        <v>-0.12339</v>
       </c>
       <c r="C178">
         <v>-70.3125</v>
@@ -14422,21 +14422,21 @@
         <v>-51.5625</v>
       </c>
       <c r="X178">
-        <v>-9.0160000000000004E-2</v>
+        <v>-9.0179999999999996E-2</v>
       </c>
       <c r="Y178">
         <v>-51.5625</v>
       </c>
       <c r="Z178">
-        <v>-9.0160000000000004E-2</v>
+        <v>-9.0139999999999998E-2</v>
       </c>
     </row>
     <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>-50</v>
+        <v>-71.875</v>
       </c>
       <c r="B179">
-        <v>-8.7279999999999996E-2</v>
+        <v>-0.12612000000000001</v>
       </c>
       <c r="C179">
         <v>-71.875</v>
@@ -14490,7 +14490,7 @@
         <v>-50</v>
       </c>
       <c r="T179">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7349999999999997E-2</v>
       </c>
       <c r="U179">
         <v>-71.875</v>
@@ -14508,15 +14508,15 @@
         <v>-50</v>
       </c>
       <c r="Z179">
-        <v>-8.7359999999999993E-2</v>
+        <v>-8.7349999999999997E-2</v>
       </c>
     </row>
     <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>-48.4375</v>
+        <v>-73.4375</v>
       </c>
       <c r="B180">
-        <v>-8.4540000000000004E-2</v>
+        <v>-0.12887999999999999</v>
       </c>
       <c r="C180">
         <v>-73.4375</v>
@@ -14582,21 +14582,21 @@
         <v>-48.4375</v>
       </c>
       <c r="X180">
-        <v>-8.4610000000000005E-2</v>
+        <v>-8.4620000000000001E-2</v>
       </c>
       <c r="Y180">
         <v>-48.4375</v>
       </c>
       <c r="Z180">
-        <v>-8.4610000000000005E-2</v>
+        <v>-8.4620000000000001E-2</v>
       </c>
     </row>
     <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>-46.875</v>
+        <v>-75</v>
       </c>
       <c r="B181">
-        <v>-8.1790000000000002E-2</v>
+        <v>-0.13161999999999999</v>
       </c>
       <c r="C181">
         <v>-75</v>
@@ -14650,7 +14650,7 @@
         <v>-46.875</v>
       </c>
       <c r="T181">
-        <v>-8.1869999999999998E-2</v>
+        <v>-8.1879999999999994E-2</v>
       </c>
       <c r="U181">
         <v>-75</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>-45.3125</v>
+        <v>-76.5625</v>
       </c>
       <c r="B182">
-        <v>-7.9030000000000003E-2</v>
+        <v>-0.13435</v>
       </c>
       <c r="C182">
         <v>-76.5625</v>
@@ -14742,21 +14742,21 @@
         <v>-45.3125</v>
       </c>
       <c r="X182">
-        <v>-7.9140000000000002E-2</v>
+        <v>-7.9149999999999998E-2</v>
       </c>
       <c r="Y182">
         <v>-45.3125</v>
       </c>
       <c r="Z182">
-        <v>-7.9119999999999996E-2</v>
+        <v>-7.9140000000000002E-2</v>
       </c>
     </row>
     <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>-43.75</v>
+        <v>-78.125</v>
       </c>
       <c r="B183">
-        <v>-7.6289999999999997E-2</v>
+        <v>-0.13711000000000001</v>
       </c>
       <c r="C183">
         <v>-78.125</v>
@@ -14822,7 +14822,7 @@
         <v>-43.75</v>
       </c>
       <c r="X183">
-        <v>-7.6380000000000003E-2</v>
+        <v>-7.6359999999999997E-2</v>
       </c>
       <c r="Y183">
         <v>-43.75</v>
@@ -14833,10 +14833,10 @@
     </row>
     <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>-42.1875</v>
+        <v>-79.6875</v>
       </c>
       <c r="B184">
-        <v>-7.356E-2</v>
+        <v>-0.13986000000000001</v>
       </c>
       <c r="C184">
         <v>-79.6875</v>
@@ -14902,21 +14902,21 @@
         <v>-42.1875</v>
       </c>
       <c r="X184">
-        <v>-7.3669999999999999E-2</v>
+        <v>-7.3679999999999995E-2</v>
       </c>
       <c r="Y184">
         <v>-42.1875</v>
       </c>
       <c r="Z184">
-        <v>-7.3649999999999993E-2</v>
+        <v>-7.3639999999999997E-2</v>
       </c>
     </row>
     <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>-40.625</v>
+        <v>-81.25</v>
       </c>
       <c r="B185">
-        <v>-7.0800000000000002E-2</v>
+        <v>-0.1426</v>
       </c>
       <c r="C185">
         <v>-81.25</v>
@@ -14982,21 +14982,21 @@
         <v>-40.625</v>
       </c>
       <c r="X185">
-        <v>-7.0910000000000001E-2</v>
+        <v>-7.0919999999999997E-2</v>
       </c>
       <c r="Y185">
         <v>-40.625</v>
       </c>
       <c r="Z185">
-        <v>-7.0930000000000007E-2</v>
+        <v>-7.0910000000000001E-2</v>
       </c>
     </row>
     <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>-39.0625</v>
+        <v>-82.8125</v>
       </c>
       <c r="B186">
-        <v>-6.8070000000000006E-2</v>
+        <v>-0.14538000000000001</v>
       </c>
       <c r="C186">
         <v>-82.8125</v>
@@ -15062,21 +15062,21 @@
         <v>-39.0625</v>
       </c>
       <c r="X186">
-        <v>-6.8180000000000004E-2</v>
+        <v>-6.8169999999999994E-2</v>
       </c>
       <c r="Y186">
         <v>-39.0625</v>
       </c>
       <c r="Z186">
-        <v>-6.8180000000000004E-2</v>
+        <v>-6.8169999999999994E-2</v>
       </c>
     </row>
     <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>-37.5</v>
+        <v>-84.375</v>
       </c>
       <c r="B187">
-        <v>-6.5310000000000007E-2</v>
+        <v>-0.14810999999999999</v>
       </c>
       <c r="C187">
         <v>-84.375</v>
@@ -15130,7 +15130,7 @@
         <v>-37.5</v>
       </c>
       <c r="T187">
-        <v>-6.5439999999999998E-2</v>
+        <v>-6.5420000000000006E-2</v>
       </c>
       <c r="U187">
         <v>-84.375</v>
@@ -15153,10 +15153,10 @@
     </row>
     <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>-35.9375</v>
+        <v>-85.9375</v>
       </c>
       <c r="B188">
-        <v>-6.2579999999999997E-2</v>
+        <v>-0.15087</v>
       </c>
       <c r="C188">
         <v>-85.9375</v>
@@ -15228,15 +15228,15 @@
         <v>-35.9375</v>
       </c>
       <c r="Z188">
-        <v>-6.2689999999999996E-2</v>
+        <v>-6.2719999999999998E-2</v>
       </c>
     </row>
     <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>-34.375</v>
+        <v>-87.5</v>
       </c>
       <c r="B189">
-        <v>-5.9819999999999998E-2</v>
+        <v>-0.15362000000000001</v>
       </c>
       <c r="C189">
         <v>-87.5</v>
@@ -15302,7 +15302,7 @@
         <v>-34.375</v>
       </c>
       <c r="X189">
-        <v>-5.9929999999999997E-2</v>
+        <v>-5.9909999999999998E-2</v>
       </c>
       <c r="Y189">
         <v>-34.375</v>
@@ -15313,10 +15313,10 @@
     </row>
     <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>-32.8125</v>
+        <v>-89.0625</v>
       </c>
       <c r="B190">
-        <v>-5.706E-2</v>
+        <v>-0.15636</v>
       </c>
       <c r="C190">
         <v>-89.0625</v>
@@ -15393,10 +15393,10 @@
     </row>
     <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>-31.25</v>
+        <v>-90.625</v>
       </c>
       <c r="B191">
-        <v>-5.4179999999999999E-2</v>
+        <v>-0.15914</v>
       </c>
       <c r="C191">
         <v>-90.625</v>
@@ -15462,21 +15462,21 @@
         <v>-31.25</v>
       </c>
       <c r="X191">
-        <v>-5.4480000000000001E-2</v>
+        <v>-5.4489999999999997E-2</v>
       </c>
       <c r="Y191">
         <v>-31.25</v>
       </c>
       <c r="Z191">
-        <v>-5.4480000000000001E-2</v>
+        <v>-5.45E-2</v>
       </c>
     </row>
     <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>-29.6875</v>
+        <v>-92.1875</v>
       </c>
       <c r="B192">
-        <v>-5.0650000000000001E-2</v>
+        <v>-0.16189000000000001</v>
       </c>
       <c r="C192">
         <v>-92.1875</v>
@@ -15542,7 +15542,7 @@
         <v>-29.6875</v>
       </c>
       <c r="X192">
-        <v>-5.1720000000000002E-2</v>
+        <v>-5.1729999999999998E-2</v>
       </c>
       <c r="Y192">
         <v>-29.6875</v>
@@ -15553,10 +15553,10 @@
     </row>
     <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>-28.125</v>
+        <v>-93.75</v>
       </c>
       <c r="B193">
-        <v>-4.5289999999999997E-2</v>
+        <v>-0.16464999999999999</v>
       </c>
       <c r="C193">
         <v>-93.75</v>
@@ -15622,21 +15622,21 @@
         <v>-28.125</v>
       </c>
       <c r="X193">
-        <v>-4.8989999999999999E-2</v>
+        <v>-4.895E-2</v>
       </c>
       <c r="Y193">
         <v>-28.125</v>
       </c>
       <c r="Z193">
-        <v>-4.8840000000000001E-2</v>
+        <v>-4.8849999999999998E-2</v>
       </c>
     </row>
     <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>-26.5625</v>
+        <v>-95.3125</v>
       </c>
       <c r="B194">
-        <v>-3.6799999999999999E-2</v>
+        <v>-0.16739999999999999</v>
       </c>
       <c r="C194">
         <v>-95.3125</v>
@@ -15713,10 +15713,10 @@
     </row>
     <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>-25</v>
+        <v>-96.875</v>
       </c>
       <c r="B195">
-        <v>-5.1000000000000004E-3</v>
+        <v>-0.17016000000000001</v>
       </c>
       <c r="C195">
         <v>-96.875</v>
@@ -15782,7 +15782,7 @@
         <v>-25</v>
       </c>
       <c r="X195">
-        <v>-4.3499999999999997E-2</v>
+        <v>-4.3479999999999998E-2</v>
       </c>
       <c r="Y195">
         <v>-25</v>
@@ -15793,10 +15793,10 @@
     </row>
     <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>-23.4375</v>
+        <v>-98.4375</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>-0.17294000000000001</v>
       </c>
       <c r="C196">
         <v>-98.4375</v>
@@ -15862,7 +15862,7 @@
         <v>-23.4375</v>
       </c>
       <c r="X196">
-        <v>-4.0739999999999998E-2</v>
+        <v>-4.0759999999999998E-2</v>
       </c>
       <c r="Y196">
         <v>-23.4375</v>
@@ -15873,10 +15873,10 @@
     </row>
     <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>-21.875</v>
+        <v>-100</v>
       </c>
       <c r="B197">
-        <v>0</v>
+        <v>-0.17533000000000001</v>
       </c>
       <c r="C197">
         <v>-100</v>
@@ -15942,7 +15942,7 @@
         <v>-21.875</v>
       </c>
       <c r="X197">
-        <v>-3.7859999999999998E-2</v>
+        <v>-3.7879999999999997E-2</v>
       </c>
       <c r="Y197">
         <v>-21.875</v>
@@ -15953,10 +15953,10 @@
     </row>
     <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>-20.3125</v>
+        <v>-98.4375</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>-0.17257</v>
       </c>
       <c r="C198">
         <v>-98.4375</v>
@@ -16022,7 +16022,7 @@
         <v>-20.3125</v>
       </c>
       <c r="X198">
-        <v>-3.456E-2</v>
+        <v>-3.4549999999999997E-2</v>
       </c>
       <c r="Y198">
         <v>-20.3125</v>
@@ -16033,10 +16033,10 @@
     </row>
     <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>-18.75</v>
+        <v>-96.875</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>-0.16982</v>
       </c>
       <c r="C199">
         <v>-96.875</v>
@@ -16102,7 +16102,7 @@
         <v>-18.75</v>
       </c>
       <c r="X199">
-        <v>-3.0339999999999999E-2</v>
+        <v>-3.0360000000000002E-2</v>
       </c>
       <c r="Y199">
         <v>-18.75</v>
@@ -16113,10 +16113,10 @@
     </row>
     <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>-17.1875</v>
+        <v>-95.3125</v>
       </c>
       <c r="B200">
-        <v>0</v>
+        <v>-0.16705999999999999</v>
       </c>
       <c r="C200">
         <v>-95.3125</v>
@@ -16193,10 +16193,10 @@
     </row>
     <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>-15.625</v>
+        <v>-93.75</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>-0.1643</v>
       </c>
       <c r="C201">
         <v>-93.75</v>
@@ -16273,10 +16273,10 @@
     </row>
     <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>-14.0625</v>
+        <v>-92.1875</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>-0.16156999999999999</v>
       </c>
       <c r="C202">
         <v>-92.1875</v>
@@ -16353,10 +16353,10 @@
     </row>
     <row r="203" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>-12.5</v>
+        <v>-90.625</v>
       </c>
       <c r="B203">
-        <v>0</v>
+        <v>-0.15878999999999999</v>
       </c>
       <c r="C203">
         <v>-90.625</v>
@@ -16433,10 +16433,10 @@
     </row>
     <row r="204" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>-10.9375</v>
+        <v>-89.0625</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>-0.15606</v>
       </c>
       <c r="C204">
         <v>-89.0625</v>
@@ -16448,7 +16448,7 @@
         <v>-89.0625</v>
       </c>
       <c r="F204">
-        <v>-0.15601000000000001</v>
+        <v>-0.15601999999999999</v>
       </c>
       <c r="G204">
         <v>-89.0625</v>
@@ -16513,16 +16513,16 @@
     </row>
     <row r="205" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>-9.375</v>
+        <v>-87.5</v>
       </c>
       <c r="B205">
-        <v>0</v>
+        <v>-0.15329999999999999</v>
       </c>
       <c r="C205">
         <v>-87.5</v>
       </c>
       <c r="D205">
-        <v>-0.15326000000000001</v>
+        <v>-0.15325</v>
       </c>
       <c r="E205">
         <v>-87.5</v>
@@ -16593,10 +16593,10 @@
     </row>
     <row r="206" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>-7.8125</v>
+        <v>-85.9375</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>-0.15054000000000001</v>
       </c>
       <c r="C206">
         <v>-85.9375</v>
@@ -16608,7 +16608,7 @@
         <v>-85.9375</v>
       </c>
       <c r="F206">
-        <v>-0.15049999999999999</v>
+        <v>-0.15051</v>
       </c>
       <c r="G206">
         <v>-85.9375</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="207" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>-6.25</v>
+        <v>-84.375</v>
       </c>
       <c r="B207">
-        <v>0</v>
+        <v>-0.14779</v>
       </c>
       <c r="C207">
         <v>-84.375</v>
@@ -16753,10 +16753,10 @@
     </row>
     <row r="208" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>-4.6875</v>
+        <v>-82.8125</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>-0.14502999999999999</v>
       </c>
       <c r="C208">
         <v>-82.8125</v>
@@ -16833,16 +16833,16 @@
     </row>
     <row r="209" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>-3.125</v>
+        <v>-81.25</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>-0.14230000000000001</v>
       </c>
       <c r="C209">
         <v>-81.25</v>
       </c>
       <c r="D209">
-        <v>-0.14227000000000001</v>
+        <v>-0.14227999999999999</v>
       </c>
       <c r="E209">
         <v>-81.25</v>
@@ -16913,10 +16913,10 @@
     </row>
     <row r="210" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>-1.5625</v>
+        <v>-79.6875</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>-0.13954</v>
       </c>
       <c r="C210">
         <v>-79.6875</v>
@@ -16992,6 +16992,12 @@
       </c>
     </row>
     <row r="211" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>-78.125</v>
+      </c>
+      <c r="B211">
+        <v>-0.1368</v>
+      </c>
       <c r="C211">
         <v>-78.125</v>
       </c>
@@ -17036,6 +17042,12 @@
       </c>
     </row>
     <row r="212" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>-76.5625</v>
+      </c>
+      <c r="B212">
+        <v>-0.13403000000000001</v>
+      </c>
       <c r="C212">
         <v>-76.5625</v>
       </c>
@@ -17080,6 +17092,12 @@
       </c>
     </row>
     <row r="213" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>-75</v>
+      </c>
+      <c r="B213">
+        <v>-0.13128999999999999</v>
+      </c>
       <c r="C213">
         <v>-75</v>
       </c>
@@ -17124,6 +17142,12 @@
       </c>
     </row>
     <row r="214" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>-73.4375</v>
+      </c>
+      <c r="B214">
+        <v>-0.12856000000000001</v>
+      </c>
       <c r="C214">
         <v>-73.4375</v>
       </c>
@@ -17168,6 +17192,12 @@
       </c>
     </row>
     <row r="215" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>-71.875</v>
+      </c>
+      <c r="B215">
+        <v>-0.1258</v>
+      </c>
       <c r="C215">
         <v>-71.875</v>
       </c>
@@ -17212,6 +17242,12 @@
       </c>
     </row>
     <row r="216" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>-70.3125</v>
+      </c>
+      <c r="B216">
+        <v>-0.12304</v>
+      </c>
       <c r="C216">
         <v>-70.3125</v>
       </c>
@@ -17256,6 +17292,12 @@
       </c>
     </row>
     <row r="217" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>-68.75</v>
+      </c>
+      <c r="B217">
+        <v>-0.12033000000000001</v>
+      </c>
       <c r="C217">
         <v>-68.75</v>
       </c>
@@ -17300,6 +17342,12 @@
       </c>
     </row>
     <row r="218" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>-67.1875</v>
+      </c>
+      <c r="B218">
+        <v>-0.11755</v>
+      </c>
       <c r="C218">
         <v>-67.1875</v>
       </c>
@@ -17344,6 +17392,12 @@
       </c>
     </row>
     <row r="219" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>-65.625</v>
+      </c>
+      <c r="B219">
+        <v>-0.11482000000000001</v>
+      </c>
       <c r="C219">
         <v>-65.625</v>
       </c>
@@ -17388,6 +17442,12 @@
       </c>
     </row>
     <row r="220" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>-64.0625</v>
+      </c>
+      <c r="B220">
+        <v>-0.11206000000000001</v>
+      </c>
       <c r="C220">
         <v>-64.0625</v>
       </c>
@@ -17432,6 +17492,12 @@
       </c>
     </row>
     <row r="221" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>-62.5</v>
+      </c>
+      <c r="B221">
+        <v>-0.10931</v>
+      </c>
       <c r="C221">
         <v>-62.5</v>
       </c>
@@ -17476,6 +17542,12 @@
       </c>
     </row>
     <row r="222" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>-60.9375</v>
+      </c>
+      <c r="B222">
+        <v>-0.10657</v>
+      </c>
       <c r="C222">
         <v>-60.9375</v>
       </c>
@@ -17520,6 +17592,12 @@
       </c>
     </row>
     <row r="223" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>-59.375</v>
+      </c>
+      <c r="B223">
+        <v>-0.10384</v>
+      </c>
       <c r="C223">
         <v>-59.375</v>
       </c>
@@ -17564,6 +17642,12 @@
       </c>
     </row>
     <row r="224" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>-57.8125</v>
+      </c>
+      <c r="B224">
+        <v>-0.10108</v>
+      </c>
       <c r="C224">
         <v>-57.8125</v>
       </c>
@@ -17607,7 +17691,13 @@
         <v>-0.10112</v>
       </c>
     </row>
-    <row r="225" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>-56.25</v>
+      </c>
+      <c r="B225">
+        <v>-9.8350000000000007E-2</v>
+      </c>
       <c r="C225">
         <v>-56.25</v>
       </c>
@@ -17651,7 +17741,13 @@
         <v>-9.8369999999999999E-2</v>
       </c>
     </row>
-    <row r="226" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>-54.6875</v>
+      </c>
+      <c r="B226">
+        <v>-9.5589999999999994E-2</v>
+      </c>
       <c r="C226">
         <v>-54.6875</v>
       </c>
@@ -17695,7 +17791,13 @@
         <v>-9.5649999999999999E-2</v>
       </c>
     </row>
-    <row r="227" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>-53.125</v>
+      </c>
+      <c r="B227">
+        <v>-9.2850000000000002E-2</v>
+      </c>
       <c r="C227">
         <v>-53.125</v>
       </c>
@@ -17739,7 +17841,13 @@
         <v>-9.2899999999999996E-2</v>
       </c>
     </row>
-    <row r="228" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>-51.5625</v>
+      </c>
+      <c r="B228">
+        <v>-9.0120000000000006E-2</v>
+      </c>
       <c r="C228">
         <v>-51.5625</v>
       </c>
@@ -17783,7 +17891,13 @@
         <v>-9.0160000000000004E-2</v>
       </c>
     </row>
-    <row r="229" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>-50</v>
+      </c>
+      <c r="B229">
+        <v>-8.7279999999999996E-2</v>
+      </c>
       <c r="C229">
         <v>-50</v>
       </c>
@@ -17827,7 +17941,13 @@
         <v>-8.7340000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>-48.4375</v>
+      </c>
+      <c r="B230">
+        <v>-8.4540000000000004E-2</v>
+      </c>
       <c r="C230">
         <v>-48.4375</v>
       </c>
@@ -17871,7 +17991,13 @@
         <v>-8.4610000000000005E-2</v>
       </c>
     </row>
-    <row r="231" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>-46.875</v>
+      </c>
+      <c r="B231">
+        <v>-8.1790000000000002E-2</v>
+      </c>
       <c r="C231">
         <v>-46.875</v>
       </c>
@@ -17915,7 +18041,13 @@
         <v>-8.1850000000000006E-2</v>
       </c>
     </row>
-    <row r="232" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>-45.3125</v>
+      </c>
+      <c r="B232">
+        <v>-7.9030000000000003E-2</v>
+      </c>
       <c r="C232">
         <v>-45.3125</v>
       </c>
@@ -17959,7 +18091,13 @@
         <v>-7.9140000000000002E-2</v>
       </c>
     </row>
-    <row r="233" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>-43.75</v>
+      </c>
+      <c r="B233">
+        <v>-7.6289999999999997E-2</v>
+      </c>
       <c r="C233">
         <v>-43.75</v>
       </c>
@@ -18003,7 +18141,13 @@
         <v>-7.6380000000000003E-2</v>
       </c>
     </row>
-    <row r="234" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>-42.1875</v>
+      </c>
+      <c r="B234">
+        <v>-7.356E-2</v>
+      </c>
       <c r="C234">
         <v>-42.1875</v>
       </c>
@@ -18047,7 +18191,13 @@
         <v>-7.3649999999999993E-2</v>
       </c>
     </row>
-    <row r="235" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>-40.625</v>
+      </c>
+      <c r="B235">
+        <v>-7.0800000000000002E-2</v>
+      </c>
       <c r="C235">
         <v>-40.625</v>
       </c>
@@ -18091,7 +18241,13 @@
         <v>-7.0889999999999995E-2</v>
       </c>
     </row>
-    <row r="236" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>-39.0625</v>
+      </c>
+      <c r="B236">
+        <v>-6.8070000000000006E-2</v>
+      </c>
       <c r="C236">
         <v>-39.0625</v>
       </c>
@@ -18135,7 +18291,13 @@
         <v>-6.8180000000000004E-2</v>
       </c>
     </row>
-    <row r="237" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>-37.5</v>
+      </c>
+      <c r="B237">
+        <v>-6.5310000000000007E-2</v>
+      </c>
       <c r="C237">
         <v>-37.5</v>
       </c>
@@ -18179,7 +18341,13 @@
         <v>-6.54E-2</v>
       </c>
     </row>
-    <row r="238" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>-35.9375</v>
+      </c>
+      <c r="B238">
+        <v>-6.2579999999999997E-2</v>
+      </c>
       <c r="C238">
         <v>-35.9375</v>
       </c>
@@ -18223,7 +18391,13 @@
         <v>-6.2689999999999996E-2</v>
       </c>
     </row>
-    <row r="239" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>-34.375</v>
+      </c>
+      <c r="B239">
+        <v>-5.9819999999999998E-2</v>
+      </c>
       <c r="C239">
         <v>-34.375</v>
       </c>
@@ -18267,7 +18441,13 @@
         <v>-5.9909999999999998E-2</v>
       </c>
     </row>
-    <row r="240" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>-32.8125</v>
+      </c>
+      <c r="B240">
+        <v>-5.706E-2</v>
+      </c>
       <c r="C240">
         <v>-32.8125</v>
       </c>
@@ -18311,7 +18491,13 @@
         <v>-5.7169999999999999E-2</v>
       </c>
     </row>
-    <row r="241" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>-31.25</v>
+      </c>
+      <c r="B241">
+        <v>-5.4179999999999999E-2</v>
+      </c>
       <c r="C241">
         <v>-31.25</v>
       </c>
@@ -18355,7 +18541,13 @@
         <v>-5.491E-2</v>
       </c>
     </row>
-    <row r="242" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>-29.6875</v>
+      </c>
+      <c r="B242">
+        <v>-5.0650000000000001E-2</v>
+      </c>
       <c r="C242">
         <v>-29.6875</v>
       </c>
@@ -18399,7 +18591,13 @@
         <v>-5.2310000000000002E-2</v>
       </c>
     </row>
-    <row r="243" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>-28.125</v>
+      </c>
+      <c r="B243">
+        <v>-4.5289999999999997E-2</v>
+      </c>
       <c r="C243">
         <v>-28.125</v>
       </c>
@@ -18443,7 +18641,13 @@
         <v>-4.9579999999999999E-2</v>
       </c>
     </row>
-    <row r="244" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>-26.5625</v>
+      </c>
+      <c r="B244">
+        <v>-3.6799999999999999E-2</v>
+      </c>
       <c r="C244">
         <v>-26.5625</v>
       </c>
@@ -18487,7 +18691,13 @@
         <v>-4.657E-2</v>
       </c>
     </row>
-    <row r="245" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>-25</v>
+      </c>
+      <c r="B245">
+        <v>-5.1000000000000004E-3</v>
+      </c>
       <c r="C245">
         <v>-25</v>
       </c>
@@ -18531,7 +18741,13 @@
         <v>-4.367E-2</v>
       </c>
     </row>
-    <row r="246" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>-23.4375</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
       <c r="C246">
         <v>-23.4375</v>
       </c>
@@ -18575,7 +18791,13 @@
         <v>-4.1419999999999998E-2</v>
       </c>
     </row>
-    <row r="247" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>-21.875</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
       <c r="C247">
         <v>-21.875</v>
       </c>
@@ -18619,7 +18841,13 @@
         <v>-3.7650000000000003E-2</v>
       </c>
     </row>
-    <row r="248" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>-20.3125</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
       <c r="C248">
         <v>-20.3125</v>
       </c>
@@ -18663,7 +18891,13 @@
         <v>-3.4639999999999997E-2</v>
       </c>
     </row>
-    <row r="249" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>-18.75</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
       <c r="C249">
         <v>-18.75</v>
       </c>
@@ -18707,7 +18941,13 @@
         <v>-3.0870000000000002E-2</v>
       </c>
     </row>
-    <row r="250" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>-17.1875</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
       <c r="C250">
         <v>-17.1875</v>
       </c>
@@ -18751,7 +18991,13 @@
         <v>-2.6349999999999998E-2</v>
       </c>
     </row>
-    <row r="251" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>-15.625</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
       <c r="C251">
         <v>-15.625</v>
       </c>
@@ -18795,7 +19041,13 @@
         <v>-1.882E-2</v>
       </c>
     </row>
-    <row r="252" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>-14.0625</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
       <c r="C252">
         <v>-14.0625</v>
       </c>
@@ -18839,7 +19091,13 @@
         <v>-6.77E-3</v>
       </c>
     </row>
-    <row r="253" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>-12.5</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
       <c r="C253">
         <v>-12.5</v>
       </c>
@@ -18883,7 +19141,13 @@
         <v>-7.4260400000000001E-4</v>
       </c>
     </row>
-    <row r="254" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>-10.9375</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
       <c r="C254">
         <v>-10.9375</v>
       </c>
@@ -18927,7 +19191,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>-9.375</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
       <c r="C255">
         <v>-9.375</v>
       </c>
@@ -18971,7 +19241,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>-7.8125</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
       <c r="C256">
         <v>-7.8125</v>
       </c>
@@ -19015,7 +19291,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>-6.25</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
       <c r="C257">
         <v>-6.25</v>
       </c>
@@ -19059,7 +19341,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>-4.6875</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
       <c r="C258">
         <v>-4.6875</v>
       </c>
@@ -19103,7 +19391,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>-3.125</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
       <c r="C259">
         <v>-3.125</v>
       </c>
@@ -19147,7 +19441,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>-1.5625</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
       <c r="C260">
         <v>-1.5625</v>
       </c>
